--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52497AF4-94A3-451E-9DD2-34E0986A73E2}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8924EA92-5618-4380-97B9-571D3E6224B9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Practice 15APR" sheetId="1" r:id="rId1"/>
+    <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
+    <sheet name="COUNTIF,IFs" sheetId="2" r:id="rId2"/>
+    <sheet name="V,H,XLOOKUP" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="75">
   <si>
     <t>Data for Practice</t>
   </si>
@@ -162,13 +164,115 @@
   </si>
   <si>
     <t>Avg. range followed by rpimary condition and then secondary condition</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Conunt only count numeric values and ignore text, blanks and symbols</t>
+  </si>
+  <si>
+    <t>Count all non empty cells eg. date, symbols, formula that return text</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>Countl only the empty cells in range</t>
+  </si>
+  <si>
+    <t>COUNTBLANK can be used with IF</t>
+  </si>
+  <si>
+    <t>IF followed by COUNTBLANK range to check followed by condition followed by the condition value</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <t>COUNTA</t>
+  </si>
+  <si>
+    <t>COUNTBLANK</t>
+  </si>
+  <si>
+    <t>IF and COUNTBLANK</t>
+  </si>
+  <si>
+    <t>For Part 1</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Delivered</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Count the number of oders pending</t>
+  </si>
+  <si>
+    <t>Count no of people above age 30</t>
+  </si>
+  <si>
+    <t>Count no of male</t>
+  </si>
+  <si>
+    <t>COUNTIF followed by condition range followed by condition</t>
+  </si>
+  <si>
+    <t>Count no of orders deliverd in west region</t>
+  </si>
+  <si>
+    <t>COUNTIFS followed by condition range1 followed by condition1 the condition range2 followed by condition2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,8 +308,29 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,8 +367,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -279,11 +416,227 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -336,6 +689,125 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1069,4 +1541,971 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D628999E-1101-4859-A1BA-0F620A8FCB3D}">
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="4" width="14" style="23"/>
+    <col min="5" max="7" width="12.21875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" style="23" customWidth="1"/>
+    <col min="9" max="10" width="29.44140625" style="23" customWidth="1"/>
+    <col min="11" max="16384" width="14" style="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="29"/>
+      <c r="F2" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="33">
+        <v>30</v>
+      </c>
+      <c r="C3" s="33">
+        <v>500</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="29"/>
+      <c r="F3" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="35">
+        <f>COUNT(B3:B12)</f>
+        <v>8</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="33">
+        <v>28</v>
+      </c>
+      <c r="C4" s="33">
+        <v>650</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="29"/>
+      <c r="F4" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="35">
+        <f>COUNTA(B3:B12)</f>
+        <v>9</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="33">
+        <v>500</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="29"/>
+      <c r="F5" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="35">
+        <f>COUNTBLANK(B3:B12)</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="33">
+        <v>35</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="35" t="str">
+        <f>IF(COUNTBLANK(C3:C12)&gt;0,"Data Missing","No Data Missing")</f>
+        <v>Data Missing</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="33">
+        <v>32</v>
+      </c>
+      <c r="C7" s="33">
+        <v>650</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="33">
+        <v>29</v>
+      </c>
+      <c r="C8" s="33">
+        <v>700</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="38"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33">
+        <v>550</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="39"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="33">
+        <v>31</v>
+      </c>
+      <c r="C10" s="33">
+        <v>650</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="39"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="33">
+        <v>40</v>
+      </c>
+      <c r="C11" s="33">
+        <v>800</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="39"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="33">
+        <v>34</v>
+      </c>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="39"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+    </row>
+    <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="33">
+        <v>30</v>
+      </c>
+      <c r="C18" s="33">
+        <v>500</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="55">
+        <f>COUNTIF(B18:B27,"&gt;30")</f>
+        <v>6</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="62"/>
+    </row>
+    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="33">
+        <v>28</v>
+      </c>
+      <c r="C19" s="33">
+        <v>650</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="55">
+        <f>COUNTIF(E18:E27,"Male")</f>
+        <v>5</v>
+      </c>
+      <c r="H19" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="62"/>
+    </row>
+    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="33">
+        <v>35</v>
+      </c>
+      <c r="C20" s="33">
+        <v>500</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="56"/>
+      <c r="G20" s="57"/>
+    </row>
+    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="33">
+        <v>40</v>
+      </c>
+      <c r="C21" s="33">
+        <v>750</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
+    </row>
+    <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="33">
+        <v>32</v>
+      </c>
+      <c r="C22" s="33">
+        <v>650</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="56"/>
+      <c r="G22" s="57"/>
+    </row>
+    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="33">
+        <v>29</v>
+      </c>
+      <c r="C23" s="33">
+        <v>700</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="56"/>
+      <c r="G23" s="57"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="33">
+        <v>31</v>
+      </c>
+      <c r="C24" s="33">
+        <v>550</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="56"/>
+      <c r="G24" s="57"/>
+    </row>
+    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="33">
+        <v>27</v>
+      </c>
+      <c r="C25" s="33">
+        <v>650</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="56"/>
+      <c r="G25" s="57"/>
+    </row>
+    <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="33">
+        <v>45</v>
+      </c>
+      <c r="C26" s="33">
+        <v>800</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="56"/>
+      <c r="G26" s="57"/>
+    </row>
+    <row r="27" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="33">
+        <v>34</v>
+      </c>
+      <c r="C27" s="33">
+        <v>700</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="58"/>
+      <c r="G27" s="59"/>
+    </row>
+    <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="45"/>
+    </row>
+    <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="47"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="69"/>
+    </row>
+    <row r="33" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="33">
+        <v>3</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="76">
+        <f>COUNTIF(D33:D51,"Pending")</f>
+        <v>7</v>
+      </c>
+      <c r="F33" s="70" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="71"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J33" s="62"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="33">
+        <v>5</v>
+      </c>
+      <c r="D34" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" s="77">
+        <f>COUNTIFS(B33:B51,"West",D33:D51,"Delivered")</f>
+        <v>3</v>
+      </c>
+      <c r="F34" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" s="74"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="J34" s="64"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="33">
+        <v>2</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="29"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="64"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="33">
+        <v>4</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="29"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="60"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="33">
+        <v>6</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="29"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="60"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="33">
+        <v>3</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="29"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="60"/>
+    </row>
+    <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="33">
+        <v>1</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="29"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="60"/>
+    </row>
+    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="33">
+        <v>5</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="29"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="60"/>
+    </row>
+    <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="33">
+        <v>2</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="29"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="60"/>
+    </row>
+    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="33">
+        <v>4</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="29"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="60"/>
+    </row>
+    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="33">
+        <v>3</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="29"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="60"/>
+    </row>
+    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="33">
+        <v>2</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="29"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="60"/>
+    </row>
+    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="33">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="29"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+    </row>
+    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="33">
+        <v>6</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="29"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="33">
+        <v>4</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" s="29"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+    </row>
+    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="33">
+        <v>3</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="29"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+    </row>
+    <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="33">
+        <v>5</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="29"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+    </row>
+    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="33">
+        <v>2</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50" s="29"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+    </row>
+    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="33">
+        <v>2</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="29"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I34:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A16:G16"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB6F217-8C78-44CE-86A6-18C085457C6F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA74B8E-F6A0-4510-98E1-CC4DB79B52AF}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861B0006-7223-4AA4-8A2B-116CAB55E18D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
     <sheet name="COUNTIF,IFs" sheetId="2" r:id="rId2"/>
     <sheet name="V,HLOOKUP" sheetId="3" r:id="rId3"/>
+    <sheet name="X,INDEX,MATCH" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,8 +41,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="125">
   <si>
     <t>Data for Practice</t>
   </si>
@@ -311,6 +334,111 @@
   </si>
   <si>
     <t>VLOOKUP followed by the condition followed by the selection of table followed by return value column and 0 or 1</t>
+  </si>
+  <si>
+    <t>For All Parts</t>
+  </si>
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Units Sold</t>
+  </si>
+  <si>
+    <t>P100</t>
+  </si>
+  <si>
+    <t>P101</t>
+  </si>
+  <si>
+    <t>P102</t>
+  </si>
+  <si>
+    <t>P103</t>
+  </si>
+  <si>
+    <t>P104</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>P105</t>
+  </si>
+  <si>
+    <t>Webcam</t>
+  </si>
+  <si>
+    <t>P106</t>
+  </si>
+  <si>
+    <t>Charger</t>
+  </si>
+  <si>
+    <t>P107</t>
+  </si>
+  <si>
+    <t>P108</t>
+  </si>
+  <si>
+    <t>Headphones</t>
+  </si>
+  <si>
+    <t>P109</t>
+  </si>
+  <si>
+    <t>USB Drive</t>
+  </si>
+  <si>
+    <t>Lookup the price of P102</t>
+  </si>
+  <si>
+    <t>Lookup price of P999 that is not there</t>
+  </si>
+  <si>
+    <t>INDEX followed by selection of range then row and column.</t>
+  </si>
+  <si>
+    <t>Index of 3rd row and 2nd column</t>
+  </si>
+  <si>
+    <t>Find value in one column based on value in other column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match which position "Laptop" is in </t>
+  </si>
+  <si>
+    <t>Price of "Monitor"</t>
+  </si>
+  <si>
+    <t>MATCH follwed by criteria "Laptop"  followed by the column where the criteria is followed by the 0</t>
+  </si>
+  <si>
+    <t>VLOOKUP followed by criteria "P999" followed by where you are searching for it followed by return reference followed by the output if confition not met.</t>
+  </si>
+  <si>
+    <t>VLOOKUP followed by criteria "P102" followed by where you are searching for it followed by return reference.</t>
+  </si>
+  <si>
+    <t>INDEX followed by column range to of answer followed by MATCH followed by criteria " Monitor" followed by column range of monitor and 0</t>
+  </si>
+  <si>
+    <t>Value of cell 5 columns below A2 and 1 right to it</t>
+  </si>
+  <si>
+    <t>OFFSET followed by reference cell followed by the number of columns below followed by number of rows right to the last column</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>Return value in C5</t>
+  </si>
+  <si>
+    <t>INDIRECT followed by the cell number</t>
   </si>
 </sst>
 </file>
@@ -397,7 +525,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,8 +574,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -708,11 +842,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -810,81 +994,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -901,23 +1010,166 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1214,14 +1466,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="11" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -1383,17 +1635,17 @@
       <c r="F12" s="18"/>
     </row>
     <row r="15" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -1666,15 +1918,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1915,15 +2167,15 @@
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -1971,10 +2223,10 @@
         <f>COUNTIF(B18:B27,"&gt;30")</f>
         <v>6</v>
       </c>
-      <c r="H18" s="59" t="s">
+      <c r="H18" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="60"/>
+      <c r="I18" s="84"/>
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="29" t="s">
@@ -1999,10 +2251,10 @@
         <f>COUNTIF(E18:E27,"Male")</f>
         <v>5</v>
       </c>
-      <c r="H19" s="59" t="s">
+      <c r="H19" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="60"/>
+      <c r="I19" s="84"/>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="29" t="s">
@@ -2158,16 +2410,16 @@
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="70"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="75"/>
     </row>
     <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39" t="s">
@@ -2183,9 +2435,9 @@
         <v>62</v>
       </c>
       <c r="E32" s="40"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="63"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="87"/>
     </row>
     <row r="33" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
@@ -2204,15 +2456,15 @@
         <f>COUNTIF(D33:D51,"Pending")</f>
         <v>7</v>
       </c>
-      <c r="F33" s="71" t="s">
+      <c r="F33" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="72"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="64" t="s">
+      <c r="G33" s="77"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="60"/>
+      <c r="J33" s="84"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="29" t="s">
@@ -2231,15 +2483,15 @@
         <f>COUNTIFS(B33:B51,"West",D33:D51,"Delivered")</f>
         <v>3</v>
       </c>
-      <c r="F34" s="74" t="s">
+      <c r="F34" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="75"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="56" t="s">
+      <c r="G34" s="80"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="J34" s="56"/>
+      <c r="J34" s="91"/>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
@@ -2255,11 +2507,11 @@
         <v>64</v>
       </c>
       <c r="E35" s="25"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="56"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="91"/>
     </row>
     <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
@@ -2275,11 +2527,11 @@
         <v>64</v>
       </c>
       <c r="E36" s="25"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="54"/>
-      <c r="J36" s="55"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="89"/>
+      <c r="J36" s="90"/>
     </row>
     <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
@@ -2295,11 +2547,11 @@
         <v>66</v>
       </c>
       <c r="E37" s="25"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="55"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="90"/>
     </row>
     <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
@@ -2315,11 +2567,11 @@
         <v>64</v>
       </c>
       <c r="E38" s="25"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="55"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="90"/>
     </row>
     <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
@@ -2335,11 +2587,11 @@
         <v>64</v>
       </c>
       <c r="E39" s="25"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="54"/>
-      <c r="J39" s="55"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="90"/>
     </row>
     <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
@@ -2355,11 +2607,11 @@
         <v>66</v>
       </c>
       <c r="E40" s="25"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="54"/>
-      <c r="J40" s="55"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="90"/>
     </row>
     <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="29" t="s">
@@ -2375,11 +2627,11 @@
         <v>64</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="55"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="90"/>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
@@ -2395,11 +2647,11 @@
         <v>66</v>
       </c>
       <c r="E42" s="25"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="54"/>
-      <c r="J42" s="55"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="89"/>
+      <c r="J42" s="90"/>
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
@@ -2415,11 +2667,11 @@
         <v>64</v>
       </c>
       <c r="E43" s="25"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="54"/>
-      <c r="J43" s="55"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="89"/>
+      <c r="J43" s="90"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
@@ -2435,11 +2687,11 @@
         <v>64</v>
       </c>
       <c r="E44" s="25"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="54"/>
-      <c r="J44" s="55"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="90"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
@@ -2455,9 +2707,9 @@
         <v>66</v>
       </c>
       <c r="E45" s="25"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
@@ -2473,9 +2725,9 @@
         <v>64</v>
       </c>
       <c r="E46" s="25"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="29" t="s">
@@ -2491,9 +2743,9 @@
         <v>66</v>
       </c>
       <c r="E47" s="25"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
@@ -2509,9 +2761,9 @@
         <v>64</v>
       </c>
       <c r="E48" s="25"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
@@ -2527,9 +2779,9 @@
         <v>64</v>
       </c>
       <c r="E49" s="25"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
     </row>
     <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
@@ -2545,9 +2797,9 @@
         <v>66</v>
       </c>
       <c r="E50" s="25"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
@@ -2563,22 +2815,22 @@
         <v>64</v>
       </c>
       <c r="E51" s="25"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I34:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="F50:H50"/>
@@ -2595,16 +2847,16 @@
     <mergeCell ref="F47:H47"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I34:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2616,301 +2868,301 @@
   <dimension ref="A1:T13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" style="93" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10" style="93" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="93" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11" style="93" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="93" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="93" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="93"/>
+    <col min="1" max="1" width="10.5546875" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="65" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="65" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="92"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="84"/>
-      <c r="F2" s="85" t="s">
+      <c r="E2" s="59"/>
+      <c r="F2" s="60" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="86">
+      <c r="B3" s="61">
         <v>1000</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="61">
         <v>20</v>
       </c>
-      <c r="E3" s="84"/>
-      <c r="F3" s="87"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="62"/>
     </row>
     <row r="4" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="86">
+      <c r="B4" s="61">
         <v>600</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="61">
         <v>15</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="87">
+      <c r="E4" s="59"/>
+      <c r="F4" s="62">
         <f>VLOOKUP("Tablet",A2:D7,4,0)</f>
         <v>15</v>
       </c>
-      <c r="G4" s="93" t="s">
+      <c r="G4" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="94" t="s">
+      <c r="H4" s="96" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="96"/>
+      <c r="S4" s="96"/>
     </row>
     <row r="5" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="86">
+      <c r="B5" s="61">
         <v>800</v>
       </c>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="61">
         <v>30</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="87">
+      <c r="E5" s="59"/>
+      <c r="F5" s="62">
         <f>VLOOKUP("Smartphone",A2:D7,2,0)</f>
         <v>800</v>
       </c>
-      <c r="G5" s="93" t="s">
+      <c r="G5" s="65" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="86">
+      <c r="B6" s="61">
         <v>300</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="61">
         <v>25</v>
       </c>
-      <c r="E6" s="84"/>
-      <c r="F6" s="87"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="62"/>
     </row>
     <row r="7" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="86">
+      <c r="B7" s="61">
         <v>50</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="61">
         <v>50</v>
       </c>
-      <c r="E7" s="88"/>
-      <c r="F7" s="89"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="64"/>
     </row>
     <row r="9" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="79" t="s">
+      <c r="D10" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="79" t="s">
+      <c r="E10" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="79" t="s">
+      <c r="F10" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="95"/>
-      <c r="H10" s="78" t="s">
+      <c r="G10" s="66"/>
+      <c r="H10" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="94" t="s">
+      <c r="I10" s="96" t="s">
         <v>88</v>
       </c>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="94"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
-      <c r="R10" s="94"/>
-      <c r="S10" s="94"/>
-      <c r="T10" s="94"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="96"/>
+      <c r="Q10" s="96"/>
+      <c r="R10" s="96"/>
+      <c r="S10" s="96"/>
+      <c r="T10" s="96"/>
     </row>
     <row r="11" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="79" t="s">
+      <c r="A11" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="79">
+      <c r="B11" s="54">
         <v>1000</v>
       </c>
-      <c r="C11" s="79">
+      <c r="C11" s="54">
         <v>600</v>
       </c>
-      <c r="D11" s="79">
+      <c r="D11" s="54">
         <v>800</v>
       </c>
-      <c r="E11" s="79">
+      <c r="E11" s="54">
         <v>300</v>
       </c>
-      <c r="F11" s="79">
+      <c r="F11" s="54">
         <v>50</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="80">
+      <c r="G11" s="67"/>
+      <c r="H11" s="55">
         <f>HLOOKUP("Laptop",A10:F13,2,0)</f>
         <v>1000</v>
       </c>
       <c r="I11" s="97" t="s">
         <v>85</v>
       </c>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="94"/>
-      <c r="P11" s="94"/>
-      <c r="Q11" s="94"/>
-      <c r="R11" s="94"/>
-      <c r="S11" s="94"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96"/>
+      <c r="O11" s="96"/>
+      <c r="P11" s="96"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
+      <c r="S11" s="96"/>
     </row>
     <row r="12" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="79" t="s">
+      <c r="E12" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="79" t="s">
+      <c r="F12" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="96"/>
-      <c r="H12" s="80" t="str">
+      <c r="G12" s="67"/>
+      <c r="H12" s="55" t="str">
         <f>HLOOKUP("Tablet",A10:F13,3,0)</f>
         <v>Electronics</v>
       </c>
       <c r="I12" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="94"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
-      <c r="S12" s="94"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="96"/>
+      <c r="O12" s="96"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="96"/>
     </row>
     <row r="13" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="79">
+      <c r="B13" s="54">
         <v>20</v>
       </c>
-      <c r="C13" s="79">
+      <c r="C13" s="54">
         <v>15</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="54">
         <v>30</v>
       </c>
-      <c r="E13" s="79">
+      <c r="E13" s="54">
         <v>25</v>
       </c>
-      <c r="F13" s="79">
+      <c r="F13" s="54">
         <v>50</v>
       </c>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82">
+      <c r="G13" s="56"/>
+      <c r="H13" s="57">
         <f>HLOOKUP("Keyboard",A10:F13,4,0)</f>
         <v>50</v>
       </c>
       <c r="I13" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="94"/>
-      <c r="S13" s="94"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="96"/>
+      <c r="S13" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2923,4 +3175,428 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0BAA80A-435E-4D17-894A-492F409949A3}">
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="6" width="13.21875" style="65"/>
+    <col min="7" max="7" width="16" style="65" customWidth="1"/>
+    <col min="8" max="16384" width="13.21875" style="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="111" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="113"/>
+    </row>
+    <row r="2" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="110" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="110" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="110" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="114" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="116"/>
+      <c r="F2" s="123" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="117"/>
+    </row>
+    <row r="3" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="99" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="99" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="99">
+        <v>150</v>
+      </c>
+      <c r="D3" s="115">
+        <v>75000</v>
+      </c>
+      <c r="E3" s="122">
+        <f>_xlfn.XLOOKUP("P102",A3:A12,D3:D12)</f>
+        <v>1500</v>
+      </c>
+      <c r="F3" s="120" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="118"/>
+      <c r="H3" s="65" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="99" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="99" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="99">
+        <v>300</v>
+      </c>
+      <c r="D4" s="115">
+        <v>500</v>
+      </c>
+      <c r="E4" s="122" t="str">
+        <f>_xlfn.XLOOKUP("P999",A3:A12,C3:C12,"Not Found")</f>
+        <v>Not Found</v>
+      </c>
+      <c r="F4" s="120" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="118"/>
+      <c r="H4" s="65" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="99" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="124">
+        <v>200</v>
+      </c>
+      <c r="D5" s="115">
+        <v>1500</v>
+      </c>
+      <c r="E5" s="122" t="str">
+        <f>INDEX(A3:D12,3,2)</f>
+        <v>Keyboard</v>
+      </c>
+      <c r="F5" s="120" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="118"/>
+      <c r="H5" s="65" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="99">
+        <v>120</v>
+      </c>
+      <c r="D6" s="115">
+        <v>10000</v>
+      </c>
+      <c r="E6" s="122">
+        <f>MATCH("Laptop",B3:B12,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="120" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="118"/>
+      <c r="H6" s="65" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="99" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="99" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="99">
+        <v>180</v>
+      </c>
+      <c r="D7" s="115">
+        <v>2500</v>
+      </c>
+      <c r="E7" s="122">
+        <f>INDEX(D3:D12,MATCH("Monitor",B3:B12,0))</f>
+        <v>10000</v>
+      </c>
+      <c r="F7" s="120" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7" s="118"/>
+      <c r="H7" s="65" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="99" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="99" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="99">
+        <v>90</v>
+      </c>
+      <c r="D8" s="115">
+        <v>4000</v>
+      </c>
+      <c r="E8" s="122"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="118"/>
+      <c r="I8" s="96" t="s">
+        <v>113</v>
+      </c>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+    </row>
+    <row r="9" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="99" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="99" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="99">
+        <v>210</v>
+      </c>
+      <c r="D9" s="115">
+        <v>1200</v>
+      </c>
+      <c r="E9" s="122" t="str">
+        <f ca="1">OFFSET(A2,5,1)</f>
+        <v>Speaker</v>
+      </c>
+      <c r="F9" s="120" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="118"/>
+      <c r="H9" s="65" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="99" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="99" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="99">
+        <v>80</v>
+      </c>
+      <c r="D10" s="115">
+        <v>30000</v>
+      </c>
+      <c r="E10" s="122"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="118"/>
+    </row>
+    <row r="11" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="99" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="99">
+        <v>160</v>
+      </c>
+      <c r="D11" s="115">
+        <v>3500</v>
+      </c>
+      <c r="E11" s="125" cm="1">
+        <f t="array" aca="1" ref="E11" ca="1">INDIRECT(F2)</f>
+        <v>200</v>
+      </c>
+      <c r="F11" s="120" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" s="118"/>
+      <c r="H11" s="65" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="99" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="99" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="99">
+        <v>400</v>
+      </c>
+      <c r="D12" s="115">
+        <v>800</v>
+      </c>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="119"/>
+    </row>
+    <row r="13" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="102"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+    </row>
+    <row r="14" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="105"/>
+    </row>
+    <row r="15" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="106"/>
+      <c r="F15" s="107" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="108" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="61">
+        <v>1200</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="61">
+        <v>25</v>
+      </c>
+      <c r="E16" s="59"/>
+      <c r="F16" s="109" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="62"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="61">
+        <v>700</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="61">
+        <v>30</v>
+      </c>
+      <c r="E17" s="59"/>
+      <c r="F17" s="109" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="62"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="61">
+        <v>900</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="61">
+        <v>45</v>
+      </c>
+      <c r="E18" s="59"/>
+      <c r="F18" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="62"/>
+    </row>
+    <row r="19" spans="1:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="61">
+        <v>300</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="61">
+        <v>20</v>
+      </c>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="98"/>
+    </row>
+    <row r="20" spans="1:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="61">
+        <v>80</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="61">
+        <v>50</v>
+      </c>
+      <c r="E20" s="63"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="101"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>